--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lee/Downloads/SAM/tws_npciap/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC7FEFF-0ADD-1145-8B84-56D16C23A714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FD59B9-281B-AD43-AFD9-79B004227AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{1E839D33-3CDD-7B45-AD48-47AF77E42AA0}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$N$57</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="597">
   <si>
     <t>公司名稱</t>
   </si>
@@ -44,9 +47,6 @@
     <t>方案類別</t>
   </si>
   <si>
-    <t>公司簡稱</t>
-  </si>
-  <si>
     <t>方案名稱</t>
   </si>
   <si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>公司官網網址</t>
-  </si>
-  <si>
-    <t>新北專屬優惠價格</t>
   </si>
   <si>
     <t>大數軟體有限公司</t>
@@ -2594,6 +2591,18 @@
   </si>
   <si>
     <t>0982163003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北專屬優惠價格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司簡稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大數軟體</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2995,2460 +3004,2462 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G1" t="s">
+        <v>577</v>
+      </c>
+      <c r="H1" t="s">
+        <v>578</v>
+      </c>
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>578</v>
-      </c>
-      <c r="G1" t="s">
-        <v>579</v>
-      </c>
-      <c r="H1" t="s">
-        <v>580</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
-        <v>8</v>
-      </c>
       <c r="N1" t="s">
-        <v>9</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>590</v>
+      </c>
+      <c r="J2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
-        <v>592</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" t="s">
         <v>29</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>36</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" t="s">
+      <c r="J4" t="s">
         <v>38</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="L4" t="s">
         <v>39</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
         <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
         <v>44</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>46</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>47</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>48</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="M5" t="s">
         <v>51</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>52</v>
-      </c>
-      <c r="M5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" t="s">
         <v>55</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
         <v>57</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>58</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>59</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>60</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>61</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J6" t="s">
+      <c r="L6" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" t="s">
         <v>64</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>65</v>
-      </c>
-      <c r="M6" t="s">
-        <v>66</v>
-      </c>
-      <c r="N6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" t="s">
         <v>68</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
+        <v>579</v>
+      </c>
+      <c r="H7" t="s">
         <v>69</v>
       </c>
-      <c r="E7" t="s">
+      <c r="I7" t="s">
         <v>70</v>
       </c>
-      <c r="G7" t="s">
-        <v>581</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>71</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" t="s">
-        <v>75</v>
-      </c>
       <c r="N7" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
         <v>76</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>77</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
         <v>78</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>79</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>80</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" t="s">
         <v>81</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="J8" t="s">
+      <c r="L8" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="N8" t="s">
         <v>84</v>
-      </c>
-      <c r="L8" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" t="s">
         <v>87</v>
       </c>
-      <c r="D9" t="s">
+      <c r="G9" t="s">
         <v>88</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>89</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>90</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" t="s">
         <v>91</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
         <v>93</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="M9" t="s">
         <v>94</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>95</v>
-      </c>
-      <c r="M9" t="s">
-        <v>96</v>
-      </c>
-      <c r="N9" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" t="s">
         <v>98</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>99</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>100</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>101</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>102</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>103</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="J10" t="s">
+      <c r="L10" t="s">
         <v>105</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="M10" t="s">
         <v>106</v>
       </c>
-      <c r="L10" t="s">
+      <c r="N10" t="s">
         <v>107</v>
-      </c>
-      <c r="M10" t="s">
-        <v>108</v>
-      </c>
-      <c r="N10" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s">
         <v>110</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>111</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>112</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>113</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>114</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
         <v>115</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>117</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="M11" t="s">
         <v>118</v>
       </c>
-      <c r="L11" t="s">
+      <c r="N11" t="s">
         <v>119</v>
-      </c>
-      <c r="M11" t="s">
-        <v>120</v>
-      </c>
-      <c r="N11" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" t="s">
         <v>111</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" t="s">
         <v>122</v>
       </c>
-      <c r="F12" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
+        <v>114</v>
+      </c>
+      <c r="J12" t="s">
+        <v>115</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="H12" t="s">
+      <c r="L12" t="s">
+        <v>117</v>
+      </c>
+      <c r="M12" t="s">
+        <v>118</v>
+      </c>
+      <c r="N12" t="s">
         <v>124</v>
-      </c>
-      <c r="I12" t="s">
-        <v>116</v>
-      </c>
-      <c r="J12" t="s">
-        <v>117</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="L12" t="s">
-        <v>119</v>
-      </c>
-      <c r="M12" t="s">
-        <v>120</v>
-      </c>
-      <c r="N12" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" t="s">
         <v>127</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>128</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>129</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
+        <v>581</v>
+      </c>
+      <c r="I13" t="s">
+        <v>582</v>
+      </c>
+      <c r="J13" t="s">
         <v>130</v>
       </c>
-      <c r="G13" t="s">
+      <c r="K13" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H13" t="s">
-        <v>583</v>
-      </c>
-      <c r="I13" t="s">
-        <v>584</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="L13" t="s">
         <v>132</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="M13" t="s">
         <v>133</v>
       </c>
-      <c r="L13" t="s">
+      <c r="N13" t="s">
         <v>134</v>
-      </c>
-      <c r="M13" t="s">
-        <v>135</v>
-      </c>
-      <c r="N13" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" t="s">
         <v>137</v>
       </c>
-      <c r="D14" t="s">
+      <c r="G14" t="s">
         <v>138</v>
       </c>
-      <c r="E14" t="s">
+      <c r="H14" t="s">
         <v>139</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>140</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>141</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="J14" t="s">
+      <c r="L14" t="s">
         <v>143</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="M14" t="s">
         <v>144</v>
       </c>
-      <c r="L14" t="s">
+      <c r="N14" t="s">
         <v>145</v>
-      </c>
-      <c r="M14" t="s">
-        <v>146</v>
-      </c>
-      <c r="N14" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" t="s">
         <v>148</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>149</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>150</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>151</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>152</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>153</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
         <v>155</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="M15" t="s">
         <v>156</v>
       </c>
-      <c r="L15" t="s">
+      <c r="N15" t="s">
         <v>157</v>
-      </c>
-      <c r="M15" t="s">
-        <v>158</v>
-      </c>
-      <c r="N15" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B16">
         <v>11</v>
       </c>
       <c r="C16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" t="s">
         <v>160</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>161</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>162</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>163</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>164</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" t="s">
         <v>165</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
         <v>167</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="M16" t="s">
         <v>168</v>
       </c>
-      <c r="L16" t="s">
+      <c r="N16" t="s">
         <v>169</v>
-      </c>
-      <c r="M16" t="s">
-        <v>170</v>
-      </c>
-      <c r="N16" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B17">
         <v>12</v>
       </c>
       <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" t="s">
         <v>172</v>
       </c>
-      <c r="D17" t="s">
+      <c r="G17" t="s">
         <v>173</v>
       </c>
-      <c r="E17" t="s">
+      <c r="H17" t="s">
         <v>174</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
         <v>175</v>
       </c>
-      <c r="H17" t="s">
+      <c r="J17" t="s">
         <v>176</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="J17" t="s">
+      <c r="L17" t="s">
         <v>178</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="M17" t="s">
         <v>179</v>
       </c>
-      <c r="L17" t="s">
+      <c r="N17" t="s">
         <v>180</v>
-      </c>
-      <c r="M17" t="s">
-        <v>181</v>
-      </c>
-      <c r="N17" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B18">
         <v>13</v>
       </c>
       <c r="C18" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E18" t="s">
         <v>183</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>184</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>185</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>186</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>187</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>188</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="J18" t="s">
+      <c r="L18" t="s">
         <v>190</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="M18" t="s">
         <v>191</v>
       </c>
-      <c r="L18" t="s">
+      <c r="N18" t="s">
         <v>192</v>
-      </c>
-      <c r="M18" t="s">
-        <v>193</v>
-      </c>
-      <c r="N18" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
       <c r="E19" t="s">
+        <v>194</v>
+      </c>
+      <c r="F19" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" t="s">
         <v>196</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>197</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" t="s">
         <v>198</v>
-      </c>
-      <c r="H19" t="s">
-        <v>199</v>
-      </c>
-      <c r="I19" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D20" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" t="s">
         <v>201</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>202</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>203</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>204</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
         <v>205</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
         <v>206</v>
-      </c>
-      <c r="I20" t="s">
-        <v>207</v>
-      </c>
-      <c r="J20" t="s">
-        <v>208</v>
       </c>
       <c r="K20" s="2">
         <v>228570010</v>
       </c>
       <c r="L20" t="s">
+        <v>207</v>
+      </c>
+      <c r="M20" t="s">
+        <v>208</v>
+      </c>
+      <c r="N20" t="s">
         <v>209</v>
-      </c>
-      <c r="M20" t="s">
-        <v>210</v>
-      </c>
-      <c r="N20" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B21">
         <v>3</v>
       </c>
       <c r="C21" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" t="s">
+        <v>211</v>
+      </c>
+      <c r="E21" t="s">
         <v>212</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>213</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>214</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>215</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" t="s">
         <v>216</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>217</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="J21" t="s">
+      <c r="L21" t="s">
         <v>219</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="M21" t="s">
         <v>220</v>
       </c>
-      <c r="L21" t="s">
+      <c r="N21" t="s">
         <v>221</v>
-      </c>
-      <c r="M21" t="s">
-        <v>222</v>
-      </c>
-      <c r="N21" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
       <c r="C22" t="s">
+        <v>222</v>
+      </c>
+      <c r="D22" t="s">
+        <v>223</v>
+      </c>
+      <c r="E22" t="s">
         <v>224</v>
       </c>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
         <v>225</v>
       </c>
-      <c r="E22" t="s">
+      <c r="H22" t="s">
         <v>226</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>227</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>228</v>
       </c>
-      <c r="I22" t="s">
+      <c r="K22" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="J22" t="s">
+      <c r="L22" t="s">
         <v>230</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="M22" t="s">
         <v>231</v>
       </c>
-      <c r="L22" t="s">
+      <c r="N22" t="s">
         <v>232</v>
-      </c>
-      <c r="M22" t="s">
-        <v>233</v>
-      </c>
-      <c r="N22" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B23">
         <v>5</v>
       </c>
       <c r="C23" t="s">
+        <v>233</v>
+      </c>
+      <c r="D23" t="s">
+        <v>234</v>
+      </c>
+      <c r="E23" t="s">
         <v>235</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>236</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
+        <v>583</v>
+      </c>
+      <c r="H23" t="s">
         <v>237</v>
       </c>
-      <c r="F23" t="s">
+      <c r="I23" t="s">
         <v>238</v>
       </c>
-      <c r="G23" t="s">
-        <v>585</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
         <v>239</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="J23" t="s">
+      <c r="L23" t="s">
         <v>241</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="M23" t="s">
         <v>242</v>
       </c>
-      <c r="L23" t="s">
+      <c r="N23" t="s">
         <v>243</v>
-      </c>
-      <c r="M23" t="s">
-        <v>244</v>
-      </c>
-      <c r="N23" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" t="s">
         <v>246</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
+        <v>247</v>
+      </c>
+      <c r="G24" t="s">
         <v>248</v>
       </c>
-      <c r="E24" t="s">
+      <c r="H24" t="s">
         <v>249</v>
       </c>
-      <c r="G24" t="s">
+      <c r="I24" t="s">
         <v>250</v>
       </c>
-      <c r="H24" t="s">
+      <c r="J24" t="s">
         <v>251</v>
-      </c>
-      <c r="I24" t="s">
-        <v>252</v>
-      </c>
-      <c r="J24" t="s">
-        <v>253</v>
       </c>
       <c r="K24" s="2">
         <v>62923231</v>
       </c>
       <c r="L24" t="s">
+        <v>252</v>
+      </c>
+      <c r="M24" t="s">
+        <v>253</v>
+      </c>
+      <c r="N24" t="s">
         <v>254</v>
-      </c>
-      <c r="M24" t="s">
-        <v>255</v>
-      </c>
-      <c r="N24" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25" t="s">
+        <v>255</v>
+      </c>
+      <c r="D25" t="s">
+        <v>256</v>
+      </c>
+      <c r="E25" t="s">
         <v>257</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
+        <v>584</v>
+      </c>
+      <c r="G25" t="s">
         <v>258</v>
       </c>
-      <c r="E25" t="s">
+      <c r="H25" t="s">
         <v>259</v>
       </c>
-      <c r="F25" t="s">
-        <v>586</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
         <v>260</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
         <v>261</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="J25" t="s">
+      <c r="L25" t="s">
         <v>263</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="M25" t="s">
         <v>264</v>
       </c>
-      <c r="L25" t="s">
+      <c r="N25" t="s">
         <v>265</v>
-      </c>
-      <c r="M25" t="s">
-        <v>266</v>
-      </c>
-      <c r="N25" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26" t="s">
+        <v>266</v>
+      </c>
+      <c r="D26" t="s">
+        <v>267</v>
+      </c>
+      <c r="E26" t="s">
         <v>268</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>269</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>270</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>271</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>272</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" t="s">
         <v>273</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="J26" t="s">
+      <c r="L26" t="s">
         <v>275</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="M26" t="s">
         <v>276</v>
       </c>
-      <c r="L26" t="s">
+      <c r="N26" t="s">
         <v>277</v>
-      </c>
-      <c r="M26" t="s">
-        <v>278</v>
-      </c>
-      <c r="N26" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
+        <v>278</v>
+      </c>
+      <c r="D27" t="s">
         <v>280</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
+        <v>281</v>
+      </c>
+      <c r="G27" t="s">
         <v>282</v>
       </c>
-      <c r="E27" t="s">
+      <c r="H27" t="s">
         <v>283</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
         <v>284</v>
       </c>
-      <c r="H27" t="s">
+      <c r="J27" t="s">
         <v>285</v>
       </c>
-      <c r="I27" t="s">
+      <c r="K27" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="J27" t="s">
+      <c r="L27" t="s">
         <v>287</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="M27" t="s">
         <v>288</v>
       </c>
-      <c r="L27" t="s">
+      <c r="N27" t="s">
         <v>289</v>
-      </c>
-      <c r="M27" t="s">
-        <v>290</v>
-      </c>
-      <c r="N27" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
+        <v>290</v>
+      </c>
+      <c r="D28" t="s">
+        <v>291</v>
+      </c>
+      <c r="E28" t="s">
         <v>292</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>293</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>294</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
         <v>295</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>296</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>297</v>
       </c>
-      <c r="I28" t="s">
+      <c r="K28" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="J28" t="s">
+      <c r="L28" t="s">
         <v>299</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="M28" t="s">
         <v>300</v>
       </c>
-      <c r="L28" t="s">
+      <c r="N28" t="s">
         <v>301</v>
-      </c>
-      <c r="M28" t="s">
-        <v>302</v>
-      </c>
-      <c r="N28" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29" t="s">
+        <v>302</v>
+      </c>
+      <c r="D29" t="s">
+        <v>303</v>
+      </c>
+      <c r="E29" t="s">
         <v>304</v>
       </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>305</v>
       </c>
-      <c r="E29" t="s">
+      <c r="G29" t="s">
         <v>306</v>
       </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
         <v>307</v>
       </c>
-      <c r="G29" t="s">
+      <c r="I29" t="s">
         <v>308</v>
       </c>
-      <c r="H29" t="s">
+      <c r="J29" t="s">
         <v>309</v>
       </c>
-      <c r="I29" t="s">
+      <c r="K29" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="J29" t="s">
+      <c r="L29" t="s">
         <v>311</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="M29" t="s">
         <v>312</v>
       </c>
-      <c r="L29" t="s">
+      <c r="N29" t="s">
         <v>313</v>
-      </c>
-      <c r="M29" t="s">
-        <v>314</v>
-      </c>
-      <c r="N29" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30" t="s">
+        <v>314</v>
+      </c>
+      <c r="D30" t="s">
+        <v>315</v>
+      </c>
+      <c r="E30" t="s">
         <v>316</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>317</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>318</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" t="s">
         <v>319</v>
       </c>
-      <c r="G30" t="s">
+      <c r="I30" t="s">
         <v>320</v>
       </c>
-      <c r="H30" t="s">
+      <c r="J30" t="s">
+        <v>115</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="I30" t="s">
+      <c r="L30" t="s">
         <v>322</v>
       </c>
-      <c r="J30" t="s">
-        <v>117</v>
-      </c>
-      <c r="K30" s="2" t="s">
+      <c r="M30" t="s">
         <v>323</v>
       </c>
-      <c r="L30" t="s">
+      <c r="N30" t="s">
         <v>324</v>
-      </c>
-      <c r="M30" t="s">
-        <v>325</v>
-      </c>
-      <c r="N30" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B31">
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" t="s">
+        <v>325</v>
+      </c>
+      <c r="F31" t="s">
         <v>111</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
+        <v>326</v>
+      </c>
+      <c r="H31" t="s">
         <v>327</v>
       </c>
-      <c r="F31" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="I31" t="s">
+        <v>114</v>
+      </c>
+      <c r="J31" t="s">
+        <v>115</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="L31" t="s">
+        <v>117</v>
+      </c>
+      <c r="M31" t="s">
+        <v>118</v>
+      </c>
+      <c r="N31" t="s">
         <v>328</v>
-      </c>
-      <c r="H31" t="s">
-        <v>329</v>
-      </c>
-      <c r="I31" t="s">
-        <v>116</v>
-      </c>
-      <c r="J31" t="s">
-        <v>117</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="L31" t="s">
-        <v>119</v>
-      </c>
-      <c r="M31" t="s">
-        <v>120</v>
-      </c>
-      <c r="N31" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
         <v>10</v>
       </c>
-      <c r="D32" t="s">
-        <v>12</v>
-      </c>
       <c r="E32" t="s">
+        <v>330</v>
+      </c>
+      <c r="F32" t="s">
+        <v>331</v>
+      </c>
+      <c r="G32" t="s">
+        <v>196</v>
+      </c>
+      <c r="H32" t="s">
         <v>332</v>
       </c>
-      <c r="F32" t="s">
-        <v>333</v>
-      </c>
-      <c r="G32" t="s">
-        <v>198</v>
-      </c>
-      <c r="H32" t="s">
-        <v>334</v>
-      </c>
       <c r="I32" t="s">
+        <v>14</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J32" t="s">
+      <c r="L32" t="s">
         <v>17</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="M32" t="s">
         <v>18</v>
       </c>
-      <c r="L32" t="s">
-        <v>19</v>
-      </c>
-      <c r="M32" t="s">
-        <v>20</v>
-      </c>
       <c r="N32" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
+        <v>333</v>
+      </c>
+      <c r="D33" t="s">
+        <v>334</v>
+      </c>
+      <c r="E33" t="s">
         <v>335</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>336</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>337</v>
       </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
         <v>338</v>
       </c>
-      <c r="G33" t="s">
+      <c r="I33" t="s">
         <v>339</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" t="s">
         <v>340</v>
       </c>
-      <c r="I33" t="s">
+      <c r="K33" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="J33" t="s">
+      <c r="L33" t="s">
         <v>342</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="M33" t="s">
         <v>343</v>
       </c>
-      <c r="L33" t="s">
+      <c r="N33" t="s">
         <v>344</v>
-      </c>
-      <c r="M33" t="s">
-        <v>345</v>
-      </c>
-      <c r="N33" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B34">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E34" t="s">
+        <v>345</v>
+      </c>
+      <c r="F34" t="s">
+        <v>346</v>
+      </c>
+      <c r="G34" t="s">
         <v>347</v>
       </c>
-      <c r="F34" t="s">
-        <v>348</v>
-      </c>
-      <c r="G34" t="s">
-        <v>349</v>
-      </c>
       <c r="H34" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I34" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J34" t="s">
+        <v>130</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="L34" t="s">
         <v>132</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="M34" t="s">
         <v>133</v>
       </c>
-      <c r="L34" t="s">
+      <c r="N34" t="s">
         <v>134</v>
-      </c>
-      <c r="M34" t="s">
-        <v>135</v>
-      </c>
-      <c r="N34" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35" t="s">
+        <v>348</v>
+      </c>
+      <c r="D35" t="s">
         <v>350</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
+        <v>351</v>
+      </c>
+      <c r="F35" t="s">
         <v>352</v>
       </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>353</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
         <v>354</v>
       </c>
-      <c r="G35" t="s">
+      <c r="I35" t="s">
         <v>355</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" t="s">
         <v>356</v>
       </c>
-      <c r="I35" t="s">
+      <c r="K35" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="J35" t="s">
+      <c r="L35" t="s">
         <v>358</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="M35" t="s">
         <v>359</v>
       </c>
-      <c r="L35" t="s">
+      <c r="N35" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="M35" t="s">
-        <v>361</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36" t="s">
+        <v>348</v>
+      </c>
+      <c r="D36" t="s">
         <v>350</v>
       </c>
-      <c r="D36" t="s">
-        <v>352</v>
-      </c>
       <c r="E36" t="s">
+        <v>361</v>
+      </c>
+      <c r="F36" t="s">
+        <v>362</v>
+      </c>
+      <c r="G36" t="s">
         <v>363</v>
       </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
         <v>364</v>
       </c>
-      <c r="G36" t="s">
+      <c r="I36" t="s">
+        <v>355</v>
+      </c>
+      <c r="J36" t="s">
+        <v>356</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="H36" t="s">
+      <c r="L36" t="s">
+        <v>358</v>
+      </c>
+      <c r="M36" t="s">
+        <v>359</v>
+      </c>
+      <c r="N36" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="I36" t="s">
-        <v>357</v>
-      </c>
-      <c r="J36" t="s">
-        <v>358</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="L36" t="s">
-        <v>360</v>
-      </c>
-      <c r="M36" t="s">
-        <v>361</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B37">
         <v>3</v>
       </c>
       <c r="C37" t="s">
+        <v>367</v>
+      </c>
+      <c r="D37" t="s">
+        <v>368</v>
+      </c>
+      <c r="E37" t="s">
         <v>369</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>370</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>371</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
         <v>372</v>
       </c>
-      <c r="G37" t="s">
+      <c r="I37" t="s">
         <v>373</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>374</v>
       </c>
-      <c r="I37" t="s">
+      <c r="K37" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="J37" t="s">
+      <c r="L37" t="s">
         <v>376</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="M37" t="s">
         <v>377</v>
       </c>
-      <c r="L37" t="s">
+      <c r="N37" t="s">
         <v>378</v>
-      </c>
-      <c r="M37" t="s">
-        <v>379</v>
-      </c>
-      <c r="N37" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
       <c r="C38" t="s">
+        <v>379</v>
+      </c>
+      <c r="D38" t="s">
+        <v>380</v>
+      </c>
+      <c r="E38" t="s">
         <v>381</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>382</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>383</v>
       </c>
-      <c r="F38" t="s">
+      <c r="H38" t="s">
         <v>384</v>
       </c>
-      <c r="G38" t="s">
+      <c r="I38" t="s">
         <v>385</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" t="s">
+        <v>228</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="I38" t="s">
+      <c r="L38" t="s">
         <v>387</v>
       </c>
-      <c r="J38" t="s">
-        <v>230</v>
-      </c>
-      <c r="K38" s="2" t="s">
+      <c r="M38" t="s">
         <v>388</v>
       </c>
-      <c r="L38" t="s">
+      <c r="N38" t="s">
         <v>389</v>
-      </c>
-      <c r="M38" t="s">
-        <v>390</v>
-      </c>
-      <c r="N38" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B39">
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D39" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E39" t="s">
+        <v>390</v>
+      </c>
+      <c r="F39" t="s">
+        <v>391</v>
+      </c>
+      <c r="G39" t="s">
         <v>392</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" t="s">
         <v>393</v>
       </c>
-      <c r="G39" t="s">
+      <c r="I39" t="s">
+        <v>216</v>
+      </c>
+      <c r="J39" t="s">
+        <v>217</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="L39" t="s">
+        <v>219</v>
+      </c>
+      <c r="M39" t="s">
+        <v>220</v>
+      </c>
+      <c r="N39" t="s">
         <v>394</v>
-      </c>
-      <c r="H39" t="s">
-        <v>395</v>
-      </c>
-      <c r="I39" t="s">
-        <v>218</v>
-      </c>
-      <c r="J39" t="s">
-        <v>219</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L39" t="s">
-        <v>221</v>
-      </c>
-      <c r="M39" t="s">
-        <v>222</v>
-      </c>
-      <c r="N39" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B40">
         <v>6</v>
       </c>
       <c r="C40" t="s">
+        <v>395</v>
+      </c>
+      <c r="D40" t="s">
+        <v>396</v>
+      </c>
+      <c r="E40" t="s">
         <v>397</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>398</v>
       </c>
-      <c r="E40" t="s">
+      <c r="G40" t="s">
         <v>399</v>
       </c>
-      <c r="F40" t="s">
+      <c r="H40" t="s">
         <v>400</v>
       </c>
-      <c r="G40" t="s">
+      <c r="I40" t="s">
         <v>401</v>
       </c>
-      <c r="H40" t="s">
+      <c r="J40" t="s">
         <v>402</v>
       </c>
-      <c r="I40" t="s">
+      <c r="K40" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="J40" t="s">
+      <c r="L40" t="s">
         <v>404</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="M40" t="s">
         <v>405</v>
       </c>
-      <c r="L40" t="s">
+      <c r="N40" t="s">
         <v>406</v>
-      </c>
-      <c r="M40" t="s">
-        <v>407</v>
-      </c>
-      <c r="N40" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41" t="s">
+        <v>407</v>
+      </c>
+      <c r="D41" t="s">
         <v>409</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
+        <v>410</v>
+      </c>
+      <c r="G41" t="s">
         <v>411</v>
       </c>
-      <c r="E41" t="s">
+      <c r="H41" t="s">
         <v>412</v>
       </c>
-      <c r="G41" t="s">
+      <c r="I41" t="s">
         <v>413</v>
       </c>
-      <c r="H41" t="s">
+      <c r="J41" t="s">
         <v>414</v>
       </c>
-      <c r="I41" t="s">
+      <c r="K41" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="J41" t="s">
+      <c r="L41" t="s">
         <v>416</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="N41" t="s">
         <v>417</v>
-      </c>
-      <c r="L41" t="s">
-        <v>418</v>
-      </c>
-      <c r="N41" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E42" t="s">
+        <v>418</v>
+      </c>
+      <c r="F42" t="s">
+        <v>419</v>
+      </c>
+      <c r="G42" t="s">
         <v>420</v>
       </c>
-      <c r="F42" t="s">
+      <c r="H42" t="s">
         <v>421</v>
       </c>
-      <c r="G42" t="s">
+      <c r="I42" t="s">
+        <v>164</v>
+      </c>
+      <c r="J42" t="s">
+        <v>165</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L42" t="s">
+        <v>167</v>
+      </c>
+      <c r="M42" t="s">
+        <v>168</v>
+      </c>
+      <c r="N42" t="s">
         <v>422</v>
-      </c>
-      <c r="H42" t="s">
-        <v>423</v>
-      </c>
-      <c r="I42" t="s">
-        <v>166</v>
-      </c>
-      <c r="J42" t="s">
-        <v>167</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="L42" t="s">
-        <v>169</v>
-      </c>
-      <c r="M42" t="s">
-        <v>170</v>
-      </c>
-      <c r="N42" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B43">
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E43" t="s">
+        <v>423</v>
+      </c>
+      <c r="F43" t="s">
+        <v>424</v>
+      </c>
+      <c r="G43" t="s">
         <v>425</v>
       </c>
-      <c r="F43" t="s">
+      <c r="H43" t="s">
         <v>426</v>
       </c>
-      <c r="G43" t="s">
+      <c r="I43" t="s">
+        <v>164</v>
+      </c>
+      <c r="J43" t="s">
+        <v>165</v>
+      </c>
+      <c r="K43" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="H43" t="s">
+      <c r="L43" t="s">
+        <v>167</v>
+      </c>
+      <c r="M43" t="s">
+        <v>168</v>
+      </c>
+      <c r="N43" t="s">
         <v>428</v>
-      </c>
-      <c r="I43" t="s">
-        <v>166</v>
-      </c>
-      <c r="J43" t="s">
-        <v>167</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="L43" t="s">
-        <v>169</v>
-      </c>
-      <c r="M43" t="s">
-        <v>170</v>
-      </c>
-      <c r="N43" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B44">
         <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
+        <v>429</v>
+      </c>
+      <c r="F44" t="s">
+        <v>587</v>
+      </c>
+      <c r="G44" t="s">
+        <v>430</v>
+      </c>
+      <c r="H44" t="s">
         <v>431</v>
       </c>
-      <c r="F44" t="s">
-        <v>589</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="I44" t="s">
+        <v>164</v>
+      </c>
+      <c r="J44" t="s">
+        <v>165</v>
+      </c>
+      <c r="K44" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="H44" t="s">
+      <c r="L44" t="s">
+        <v>167</v>
+      </c>
+      <c r="M44" t="s">
+        <v>168</v>
+      </c>
+      <c r="N44" t="s">
         <v>433</v>
-      </c>
-      <c r="I44" t="s">
-        <v>166</v>
-      </c>
-      <c r="J44" t="s">
-        <v>167</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="L44" t="s">
-        <v>169</v>
-      </c>
-      <c r="M44" t="s">
-        <v>170</v>
-      </c>
-      <c r="N44" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B45">
         <v>5</v>
       </c>
       <c r="C45" t="s">
+        <v>434</v>
+      </c>
+      <c r="D45" t="s">
+        <v>435</v>
+      </c>
+      <c r="E45" t="s">
         <v>436</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
         <v>437</v>
       </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>438</v>
       </c>
-      <c r="F45" t="s">
+      <c r="H45" t="s">
         <v>439</v>
       </c>
-      <c r="G45" t="s">
+      <c r="I45" t="s">
         <v>440</v>
       </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
         <v>441</v>
       </c>
-      <c r="I45" t="s">
+      <c r="K45" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="J45" t="s">
+      <c r="L45" t="s">
         <v>443</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="M45" t="s">
         <v>444</v>
       </c>
-      <c r="L45" t="s">
+      <c r="N45" t="s">
         <v>445</v>
-      </c>
-      <c r="M45" t="s">
-        <v>446</v>
-      </c>
-      <c r="N45" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" t="s">
+        <v>446</v>
+      </c>
+      <c r="D46" t="s">
         <v>448</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
+        <v>449</v>
+      </c>
+      <c r="F46" t="s">
         <v>450</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>451</v>
       </c>
-      <c r="F46" t="s">
+      <c r="H46" t="s">
         <v>452</v>
       </c>
-      <c r="G46" t="s">
+      <c r="I46" t="s">
         <v>453</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" t="s">
+        <v>115</v>
+      </c>
+      <c r="K46" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="I46" t="s">
+      <c r="L46" t="s">
         <v>455</v>
       </c>
-      <c r="J46" t="s">
-        <v>117</v>
-      </c>
-      <c r="K46" s="2" t="s">
+      <c r="M46" t="s">
         <v>456</v>
       </c>
-      <c r="L46" t="s">
+      <c r="N46" t="s">
         <v>457</v>
-      </c>
-      <c r="M46" t="s">
-        <v>458</v>
-      </c>
-      <c r="N46" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B47">
         <v>2</v>
       </c>
       <c r="C47" t="s">
+        <v>458</v>
+      </c>
+      <c r="D47" t="s">
+        <v>459</v>
+      </c>
+      <c r="E47" t="s">
         <v>460</v>
       </c>
-      <c r="D47" t="s">
+      <c r="F47" t="s">
         <v>461</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>462</v>
       </c>
-      <c r="F47" t="s">
+      <c r="H47" t="s">
         <v>463</v>
       </c>
-      <c r="G47" t="s">
+      <c r="I47" t="s">
         <v>464</v>
       </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
         <v>465</v>
       </c>
-      <c r="I47" t="s">
+      <c r="K47" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="J47" t="s">
+      <c r="L47" t="s">
         <v>467</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="M47" t="s">
         <v>468</v>
       </c>
-      <c r="L47" t="s">
+      <c r="N47" t="s">
         <v>469</v>
-      </c>
-      <c r="M47" t="s">
-        <v>470</v>
-      </c>
-      <c r="N47" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48" t="s">
+        <v>470</v>
+      </c>
+      <c r="D48" t="s">
+        <v>471</v>
+      </c>
+      <c r="E48" t="s">
         <v>472</v>
       </c>
-      <c r="D48" t="s">
+      <c r="G48" t="s">
         <v>473</v>
       </c>
-      <c r="E48" t="s">
+      <c r="H48" t="s">
         <v>474</v>
       </c>
-      <c r="G48" t="s">
+      <c r="I48" t="s">
         <v>475</v>
       </c>
-      <c r="H48" t="s">
+      <c r="J48" t="s">
         <v>476</v>
       </c>
-      <c r="I48" t="s">
+      <c r="K48" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="J48" t="s">
+      <c r="L48" t="s">
         <v>478</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="M48" t="s">
         <v>479</v>
       </c>
-      <c r="L48" t="s">
+      <c r="N48" t="s">
         <v>480</v>
-      </c>
-      <c r="M48" t="s">
-        <v>481</v>
-      </c>
-      <c r="N48" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="s">
+        <v>481</v>
+      </c>
+      <c r="D49" t="s">
         <v>483</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
+        <v>484</v>
+      </c>
+      <c r="F49" t="s">
+        <v>588</v>
+      </c>
+      <c r="G49" t="s">
         <v>485</v>
       </c>
-      <c r="E49" t="s">
+      <c r="H49" t="s">
         <v>486</v>
       </c>
-      <c r="F49" t="s">
-        <v>590</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="I49" t="s">
         <v>487</v>
       </c>
-      <c r="H49" t="s">
+      <c r="J49" t="s">
         <v>488</v>
       </c>
-      <c r="I49" t="s">
+      <c r="K49" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="J49" t="s">
+      <c r="L49" t="s">
         <v>490</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="M49" t="s">
         <v>491</v>
       </c>
-      <c r="L49" t="s">
+      <c r="N49" t="s">
         <v>492</v>
-      </c>
-      <c r="M49" t="s">
-        <v>493</v>
-      </c>
-      <c r="N49" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50" t="s">
+        <v>493</v>
+      </c>
+      <c r="D50" t="s">
+        <v>494</v>
+      </c>
+      <c r="E50" t="s">
         <v>495</v>
       </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
         <v>496</v>
       </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>497</v>
       </c>
-      <c r="F50" t="s">
+      <c r="H50" t="s">
         <v>498</v>
       </c>
-      <c r="G50" t="s">
+      <c r="I50" t="s">
         <v>499</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>500</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="L50" t="s">
         <v>501</v>
       </c>
-      <c r="J50" t="s">
+      <c r="M50" t="s">
         <v>502</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="L50" t="s">
+      <c r="N50" t="s">
         <v>503</v>
-      </c>
-      <c r="M50" t="s">
-        <v>504</v>
-      </c>
-      <c r="N50" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51" t="s">
+        <v>504</v>
+      </c>
+      <c r="D51" t="s">
+        <v>505</v>
+      </c>
+      <c r="E51" t="s">
         <v>506</v>
       </c>
-      <c r="D51" t="s">
+      <c r="G51" t="s">
         <v>507</v>
       </c>
-      <c r="E51" t="s">
+      <c r="H51" t="s">
         <v>508</v>
       </c>
-      <c r="G51" t="s">
+      <c r="I51" t="s">
         <v>509</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>510</v>
       </c>
-      <c r="I51" t="s">
+      <c r="K51" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="J51" t="s">
+      <c r="L51" t="s">
         <v>512</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="M51" t="s">
         <v>513</v>
       </c>
-      <c r="L51" t="s">
+      <c r="N51" t="s">
         <v>514</v>
-      </c>
-      <c r="M51" t="s">
-        <v>515</v>
-      </c>
-      <c r="N51" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B52">
         <v>4</v>
       </c>
       <c r="C52" t="s">
+        <v>515</v>
+      </c>
+      <c r="D52" t="s">
+        <v>516</v>
+      </c>
+      <c r="E52" t="s">
         <v>517</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
         <v>518</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>519</v>
       </c>
-      <c r="F52" t="s">
+      <c r="H52" t="s">
         <v>520</v>
       </c>
-      <c r="G52" t="s">
+      <c r="I52" t="s">
         <v>521</v>
       </c>
-      <c r="H52" t="s">
+      <c r="J52" t="s">
         <v>522</v>
       </c>
-      <c r="I52" t="s">
+      <c r="K52" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="J52" t="s">
+      <c r="L52" t="s">
         <v>524</v>
       </c>
-      <c r="K52" s="2" t="s">
+      <c r="M52" t="s">
         <v>525</v>
       </c>
-      <c r="L52" t="s">
+      <c r="N52" t="s">
         <v>526</v>
-      </c>
-      <c r="M52" t="s">
-        <v>527</v>
-      </c>
-      <c r="N52" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B53">
         <v>5</v>
       </c>
       <c r="C53" t="s">
+        <v>527</v>
+      </c>
+      <c r="D53" t="s">
+        <v>528</v>
+      </c>
+      <c r="E53" t="s">
         <v>529</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F53" t="s">
         <v>530</v>
       </c>
-      <c r="E53" t="s">
+      <c r="G53" t="s">
         <v>531</v>
       </c>
-      <c r="F53" t="s">
+      <c r="H53" t="s">
         <v>532</v>
       </c>
-      <c r="G53" t="s">
+      <c r="I53" t="s">
         <v>533</v>
       </c>
-      <c r="H53" t="s">
+      <c r="J53" t="s">
         <v>534</v>
       </c>
-      <c r="I53" t="s">
+      <c r="K53" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="J53" t="s">
+      <c r="L53" t="s">
         <v>536</v>
       </c>
-      <c r="K53" s="2" t="s">
+      <c r="M53" t="s">
         <v>537</v>
       </c>
-      <c r="L53" t="s">
+      <c r="N53" t="s">
         <v>538</v>
-      </c>
-      <c r="M53" t="s">
-        <v>539</v>
-      </c>
-      <c r="N53" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B54">
         <v>6</v>
       </c>
       <c r="C54" t="s">
+        <v>539</v>
+      </c>
+      <c r="D54" t="s">
+        <v>540</v>
+      </c>
+      <c r="E54" t="s">
         <v>541</v>
       </c>
-      <c r="D54" t="s">
+      <c r="F54" t="s">
         <v>542</v>
       </c>
-      <c r="E54" t="s">
+      <c r="G54" t="s">
         <v>543</v>
       </c>
-      <c r="F54" t="s">
+      <c r="H54" t="s">
         <v>544</v>
       </c>
-      <c r="G54" t="s">
+      <c r="I54" t="s">
         <v>545</v>
       </c>
-      <c r="H54" t="s">
+      <c r="J54" t="s">
         <v>546</v>
       </c>
-      <c r="I54" t="s">
+      <c r="K54" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="J54" t="s">
+      <c r="L54" t="s">
         <v>548</v>
       </c>
-      <c r="K54" s="2" t="s">
+      <c r="M54" t="s">
         <v>549</v>
       </c>
-      <c r="L54" t="s">
+      <c r="N54" t="s">
         <v>550</v>
-      </c>
-      <c r="M54" t="s">
-        <v>551</v>
-      </c>
-      <c r="N54" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B55">
         <v>7</v>
       </c>
       <c r="C55" t="s">
+        <v>551</v>
+      </c>
+      <c r="D55" t="s">
+        <v>552</v>
+      </c>
+      <c r="E55" t="s">
         <v>553</v>
       </c>
-      <c r="D55" t="s">
+      <c r="G55" t="s">
         <v>554</v>
       </c>
-      <c r="E55" t="s">
+      <c r="H55" t="s">
         <v>555</v>
       </c>
-      <c r="G55" t="s">
+      <c r="I55" t="s">
         <v>556</v>
       </c>
-      <c r="H55" t="s">
+      <c r="J55" t="s">
         <v>557</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="J55" t="s">
+      <c r="L55" t="s">
         <v>559</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="M55" t="s">
         <v>560</v>
       </c>
-      <c r="L55" t="s">
+      <c r="N55" t="s">
         <v>561</v>
-      </c>
-      <c r="M55" t="s">
-        <v>562</v>
-      </c>
-      <c r="N55" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B56">
         <v>8</v>
       </c>
       <c r="C56" t="s">
+        <v>562</v>
+      </c>
+      <c r="D56" t="s">
+        <v>563</v>
+      </c>
+      <c r="E56" t="s">
         <v>564</v>
       </c>
-      <c r="D56" t="s">
+      <c r="G56" t="s">
         <v>565</v>
       </c>
-      <c r="E56" t="s">
+      <c r="H56" t="s">
+        <v>589</v>
+      </c>
+      <c r="I56" t="s">
         <v>566</v>
       </c>
-      <c r="G56" t="s">
+      <c r="J56" t="s">
+        <v>374</v>
+      </c>
+      <c r="K56" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="H56" t="s">
-        <v>591</v>
-      </c>
-      <c r="I56" t="s">
+      <c r="L56" t="s">
         <v>568</v>
       </c>
-      <c r="J56" t="s">
-        <v>376</v>
-      </c>
-      <c r="K56" s="2" t="s">
+      <c r="M56" t="s">
         <v>569</v>
       </c>
-      <c r="L56" t="s">
+      <c r="N56" t="s">
         <v>570</v>
-      </c>
-      <c r="M56" t="s">
-        <v>571</v>
-      </c>
-      <c r="N56" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B57">
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D57" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E57" t="s">
+        <v>571</v>
+      </c>
+      <c r="F57" t="s">
+        <v>572</v>
+      </c>
+      <c r="G57" t="s">
         <v>573</v>
       </c>
-      <c r="F57" t="s">
+      <c r="H57" t="s">
         <v>574</v>
       </c>
-      <c r="G57" t="s">
+      <c r="I57" t="s">
+        <v>187</v>
+      </c>
+      <c r="J57" t="s">
+        <v>188</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="L57" t="s">
+        <v>190</v>
+      </c>
+      <c r="M57" t="s">
+        <v>191</v>
+      </c>
+      <c r="N57" t="s">
         <v>575</v>
       </c>
-      <c r="H57" t="s">
-        <v>576</v>
-      </c>
-      <c r="I57" t="s">
-        <v>189</v>
-      </c>
-      <c r="J57" t="s">
-        <v>190</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="L57" t="s">
-        <v>192</v>
-      </c>
-      <c r="M57" t="s">
-        <v>193</v>
-      </c>
-      <c r="N57" t="s">
-        <v>577</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N57" xr:uid="{4463E034-8AB0-794B-B6DA-695E4821C245}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/metadata.xlsx
+++ b/metadata.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office ä½æ¯ä¸»é¡">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Ã¤Â½ÂÃ¦ÂÂ¯Ã¤Â¸Â»Ã©Â¡Â">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -126,10 +126,10 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="æ¸¸ã´ã·ãã¯ Light"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿ Light"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¦Â¸Â¸Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯ Light"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿ Light"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -178,10 +178,10 @@
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="æ¸¸ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¦Â¸Â¸Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -2959,9 +2959,8 @@
       <c r="E44" t="str">
         <v>WinEdge－各產業應用的AI邊緣運算推論系統</v>
       </c>
-      <c r="F44" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. https://drive.google.com/file/d/1IcWZXD7-V9l_RMdwBChvp7JXlGLudoff/view?usp=drive_link　_x000d_
-2. https://drive.google.com/file/d/1b0lvq-wgzLTKSM64o-c7z8IC0ptc_HAi/view?usp=drive_link</v>
+      <c r="F44" t="str">
+        <v>https://drive.google.com/file/d/1R0B9quHfH9tY5psOAgWD_NX0m2L3z7fx/view</v>
       </c>
       <c r="G44" t="str">
         <v>4.慧穩科技股份有限公司.png</v>
